--- a/Buyer_Segmentation_and_Investment_Profiling_in_Real_Estate/dataset/roadmap.xlsx
+++ b/Buyer_Segmentation_and_Investment_Profiling_in_Real_Estate/dataset/roadmap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\THE CODE\PROJECTS\Buyer_Segmentation_and_Investment_Profiling_in_Real_Estate\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E001379-0107-49C7-900F-C8B7C948F5D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{002AA5B6-7E6C-4DC0-A748-D91FDB60674D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{9A8E16FF-E85C-45EC-BA30-CCAA6B5FE037}"/>
   </bookViews>
@@ -239,7 +239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -251,51 +251,45 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -685,23 +679,23 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:5" s="2" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
     </row>
     <row r="4" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="16">
         <v>1</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="8" t="s">
         <v>0</v>
       </c>
     </row>
@@ -709,9 +703,9 @@
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="15" t="s">
+      <c r="C5" s="17"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="8" t="s">
         <v>3</v>
       </c>
     </row>
@@ -719,42 +713,42 @@
       <c r="A6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="15" t="s">
+      <c r="C6" s="18"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="8" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="11">
+      <c r="C7" s="16">
         <v>2</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="12"/>
-      <c r="D8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="14"/>
       <c r="E8" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="13"/>
-      <c r="D9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="15"/>
       <c r="E9" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="C10" s="6">
+      <c r="C10" s="5">
         <v>3</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="9" t="s">
         <v>11</v>
       </c>
       <c r="E10" s="3" t="s">
@@ -762,17 +756,17 @@
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
     </row>
     <row r="12" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="4">
         <v>3</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="10" t="s">
         <v>2</v>
       </c>
       <c r="E12" s="3" t="s">
@@ -783,7 +777,7 @@
       <c r="C13" s="4">
         <v>4</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="10" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="3" t="s">
@@ -794,7 +788,7 @@
       <c r="C14" s="4">
         <v>5</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="10" t="s">
         <v>11</v>
       </c>
       <c r="E14" s="3" t="s">
@@ -804,7 +798,7 @@
     <row r="15" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="16" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="17" spans="5:6" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F17" s="1"/>
@@ -844,12 +838,12 @@
     <row r="30" spans="5:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="C4:C5"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="C11:E11"/>
     <mergeCell ref="D7:D9"/>
     <mergeCell ref="C7:C9"/>
     <mergeCell ref="D4:D6"/>
+    <mergeCell ref="C4:C6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
